--- a/docs/hardware/Shopping_list_New_Segway.xlsx
+++ b/docs/hardware/Shopping_list_New_Segway.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28914"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Research_Assistant\2025-Segway\Procurement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="223" documentId="13_ncr:1_{D8D5082D-5509-4C68-85F8-16622996E95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E91734A0-06C0-4124-8B81-37E8D66863F8}"/>
+  <xr:revisionPtr revIDLastSave="225" documentId="13_ncr:1_{D8D5082D-5509-4C68-85F8-16622996E95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDC27E76-E4AB-4011-A048-186F2A6017BE}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{E1863549-E77E-453B-9416-76F8A454E272}"/>
   </bookViews>
@@ -622,12 +622,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -640,8 +634,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2062,12 +2062,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
       <c r="E1" s="19" t="s">
         <v>1</v>
       </c>
@@ -2113,25 +2113,25 @@
       <c r="A3" s="19">
         <v>1</v>
       </c>
-      <c r="B3" s="33">
+      <c r="B3" s="37">
         <v>8</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="37">
         <v>341.88</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="33">
+      <c r="G3" s="37">
         <v>341.88</v>
       </c>
-      <c r="H3" s="33">
+      <c r="H3" s="37">
         <f>G3*B3</f>
         <v>2735.04</v>
       </c>
@@ -2141,30 +2141,30 @@
       <c r="A4" s="19">
         <v>2</v>
       </c>
-      <c r="B4" s="33"/>
+      <c r="B4" s="37"/>
       <c r="C4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
       <c r="I4" s="30"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="19">
         <v>3</v>
       </c>
-      <c r="B5" s="33"/>
+      <c r="B5" s="37"/>
       <c r="C5" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
       <c r="I5" s="30"/>
     </row>
     <row r="6" spans="1:10">
@@ -2292,13 +2292,13 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="33">
+      <c r="A10" s="37">
         <v>8</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="37">
         <v>4</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="38" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -2319,9 +2319,9 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="57.75">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="39"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="38"/>
       <c r="D11" s="26" t="s">
         <v>28</v>
       </c>
@@ -2341,13 +2341,13 @@
       <c r="I11" s="30"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="33">
+      <c r="A12" s="37">
         <v>9</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="37">
         <v>4</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="38" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="23" t="s">
@@ -2368,9 +2368,9 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="57.75">
-      <c r="A13" s="33"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="39"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="38"/>
       <c r="D13" s="26" t="s">
         <v>31</v>
       </c>
@@ -2415,6 +2415,7 @@
         <f t="shared" si="1"/>
         <v>27.92</v>
       </c>
+      <c r="I14" s="30"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="19">
@@ -2442,15 +2443,16 @@
         <f t="shared" si="1"/>
         <v>42.08</v>
       </c>
+      <c r="I15" s="30"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="35">
+      <c r="A16" s="33">
         <v>12</v>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="33">
         <v>6</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="35" t="s">
         <v>37</v>
       </c>
       <c r="D16" s="23" t="s">
@@ -2471,9 +2473,9 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="87">
-      <c r="A17" s="36"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="38"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="36"/>
       <c r="D17" s="26" t="s">
         <v>39</v>
       </c>
@@ -3078,6 +3080,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
@@ -3087,13 +3096,6 @@
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="C12:C13"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" xr:uid="{610FF566-5526-499B-96AD-F6977A115174}"/>
@@ -3809,14 +3811,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e959a22a-8366-4d78-84c8-9bbf8de68e38">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="359abc46-0e7a-42be-9de3-58c87dbbd8be" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4021,16 +4021,18 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e959a22a-8366-4d78-84c8-9bbf8de68e38">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="359abc46-0e7a-42be-9de3-58c87dbbd8be" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A0EDA1-83C6-455F-838D-E9A52E2F4D5E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2966E65C-B73C-4DC7-A046-51AA4B0641CF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4038,5 +4040,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2966E65C-B73C-4DC7-A046-51AA4B0641CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A0EDA1-83C6-455F-838D-E9A52E2F4D5E}"/>
 </file>